--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.02236290172882</v>
+        <v>4.391133971530934</v>
       </c>
       <c r="D2" t="n">
-        <v>27.07405924813917</v>
+        <v>4.399534627822615</v>
       </c>
       <c r="E2" t="n">
-        <v>7.014254624883363</v>
+        <v>1.139816376543547</v>
       </c>
       <c r="F2" t="n">
-        <v>7.098382322068363</v>
+        <v>1.153487127336109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.482971465113709</v>
+        <v>1.053482863080978</v>
       </c>
       <c r="D3" t="n">
-        <v>6.258342752857626</v>
+        <v>1.016980697339364</v>
       </c>
       <c r="E3" t="n">
-        <v>7.014254624883363</v>
+        <v>1.139816376543547</v>
       </c>
       <c r="F3" t="n">
-        <v>7.098382322068363</v>
+        <v>1.153487127336109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.32457467698188</v>
+        <v>2.165243385009555</v>
       </c>
       <c r="D4" t="n">
-        <v>13.39937002655899</v>
+        <v>2.177397629315837</v>
       </c>
       <c r="E4" t="n">
-        <v>7.014254624883363</v>
+        <v>1.139816376543547</v>
       </c>
       <c r="F4" t="n">
-        <v>7.098382322068363</v>
+        <v>1.153487127336109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.36141836222648</v>
+        <v>2.333730483861803</v>
       </c>
       <c r="D5" t="n">
-        <v>14.29722920658226</v>
+        <v>2.323299746069617</v>
       </c>
       <c r="E5" t="n">
-        <v>7.014254624883363</v>
+        <v>1.139816376543547</v>
       </c>
       <c r="F5" t="n">
-        <v>7.098382322068363</v>
+        <v>1.153487127336109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.36362633406148</v>
+        <v>2.171589279284991</v>
       </c>
       <c r="D6" t="n">
-        <v>13.33762489891594</v>
+        <v>2.16736404607384</v>
       </c>
       <c r="E6" t="n">
-        <v>7.014254624883363</v>
+        <v>1.139816376543547</v>
       </c>
       <c r="F6" t="n">
-        <v>7.098382322068363</v>
+        <v>1.153487127336109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.28371901785567</v>
+        <v>4.271104340401547</v>
       </c>
       <c r="D7" t="n">
-        <v>26.29977661000042</v>
+        <v>4.273713699125069</v>
       </c>
       <c r="E7" t="n">
-        <v>7.014254624883363</v>
+        <v>1.139816376543547</v>
       </c>
       <c r="F7" t="n">
-        <v>7.098382322068363</v>
+        <v>1.153487127336109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.81057378343697</v>
+        <v>2.081718239808507</v>
       </c>
       <c r="D8" t="n">
-        <v>12.46164075953278</v>
+        <v>2.025016623424077</v>
       </c>
       <c r="E8" t="n">
-        <v>7.014254624883363</v>
+        <v>1.139816376543547</v>
       </c>
       <c r="F8" t="n">
-        <v>7.098382322068363</v>
+        <v>1.153487127336109</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
